--- a/assets/constructions/examples/ctd_tsmb_tuplethread.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_tuplethread.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:BB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,11 +674,36 @@
           <t>thr_id</t>
         </is>
       </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6.0SIR26WVMX</t>
+          <t>6.0SIR20WVMX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -735,13 +760,13 @@
         <v>2.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="U2" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
@@ -756,13 +781,13 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.63</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
@@ -821,11 +846,22 @@
         </is>
       </c>
       <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4.0SIR27UNVMX</t>
+          <t>6.0SIR27UNVMX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -846,7 +882,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VAR_4SIUN</t>
+          <t>VAR_6SIUN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -855,19 +891,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -879,13 +915,13 @@
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="U3" t="n">
         <v>0.75</v>
@@ -930,7 +966,7 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>VARGUS_TUPLE_SB:4</t>
+          <t>VARGUS_TUPLE_SB:6</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -968,11 +1004,22 @@
         </is>
       </c>
       <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3.0SIR32UNVMX</t>
+          <t>3.0SIR0.5ISOVMX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -993,7 +1040,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VAR_3SIUN</t>
+          <t>VAR_3SIISO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1002,7 +1049,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -1014,7 +1061,7 @@
         <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -1026,19 +1073,23 @@
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="T4" t="n">
         <v>0.8</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>F</t>
@@ -1046,17 +1097,13 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2A/2B</t>
-        </is>
-      </c>
-      <c r="Z4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>32</v>
-      </c>
+          <t>6g/6H</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>0.46</v>
+        <v>0.29</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
@@ -1115,11 +1162,22 @@
         </is>
       </c>
       <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4.0SIR0.5ISOVMX</t>
+          <t>4.0SIR24UNVMX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1140,7 +1198,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VAR_4SIISO</t>
+          <t>VAR_4SIUN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1149,7 +1207,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -1161,7 +1219,7 @@
         <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1173,23 +1231,19 @@
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>F</t>
@@ -1197,13 +1251,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>6g/6H</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+          <t>2A/2B</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>24</v>
+      </c>
       <c r="AB5" t="n">
-        <v>0.29</v>
+        <v>0.61</v>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
@@ -1262,11 +1320,22 @@
         </is>
       </c>
       <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6.0SIR0.75ISOVMX</t>
+          <t>4.0SIR26WVMX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1287,7 +1356,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VAR_6SIISO</t>
+          <t>VAR_4SIW</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1296,19 +1365,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1320,23 +1389,19 @@
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="S6" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="T6" t="n">
         <v>0.6</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V6" t="n">
         <v>0.75</v>
       </c>
-      <c r="W6" t="n">
-        <v>0.75</v>
-      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
           <t>F</t>
@@ -1344,18 +1409,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6g/6H</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>26</v>
+      </c>
       <c r="AB6" t="n">
-        <v>0.43</v>
+        <v>0.63</v>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>M60</t>
+          <t>WH55</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
@@ -1371,7 +1440,7 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>VARGUS_TUPLE_SB:6</t>
+          <t>VARGUS_TUPLE_SB:4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1409,6 +1478,25 @@
         </is>
       </c>
       <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>5828.6</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
